--- a/figures/lecture5/6345.0/634509a.xlsx
+++ b/figures/lecture5/6345.0/634509a.xlsx
@@ -17,272 +17,272 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A2712226R">Data1!$R$1:$R$10,Data1!$R$11:$R$36</definedName>
-    <definedName name="A2712226R_Data">Data1!$R$11:$R$36</definedName>
-    <definedName name="A2712226R_Latest">Data1!$R$36</definedName>
-    <definedName name="A2712228V">Data1!$H$1:$H$10,Data1!$H$11:$H$36</definedName>
-    <definedName name="A2712228V_Data">Data1!$H$11:$H$36</definedName>
-    <definedName name="A2712228V_Latest">Data1!$H$36</definedName>
-    <definedName name="A2712230F">Data1!$P$1:$P$10,Data1!$P$11:$P$36</definedName>
-    <definedName name="A2712230F_Data">Data1!$P$11:$P$36</definedName>
-    <definedName name="A2712230F_Latest">Data1!$P$36</definedName>
-    <definedName name="A2712232K">Data1!$K$1:$K$10,Data1!$K$11:$K$36</definedName>
-    <definedName name="A2712232K_Data">Data1!$K$11:$K$36</definedName>
-    <definedName name="A2712232K_Latest">Data1!$K$36</definedName>
-    <definedName name="A2712234R">Data1!$I$1:$I$10,Data1!$I$11:$I$36</definedName>
-    <definedName name="A2712234R_Data">Data1!$I$11:$I$36</definedName>
-    <definedName name="A2712234R_Latest">Data1!$I$36</definedName>
-    <definedName name="A2712236V">Data1!$M$1:$M$10,Data1!$M$11:$M$36</definedName>
-    <definedName name="A2712236V_Data">Data1!$M$11:$M$36</definedName>
-    <definedName name="A2712236V_Latest">Data1!$M$36</definedName>
-    <definedName name="A2712238X">Data1!$D$1:$D$10,Data1!$D$11:$D$36</definedName>
-    <definedName name="A2712238X_Data">Data1!$D$11:$D$36</definedName>
-    <definedName name="A2712238X_Latest">Data1!$D$36</definedName>
-    <definedName name="A2712240K">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$36</definedName>
-    <definedName name="A2712240K_Data">Data1!$Q$11:$Q$36</definedName>
-    <definedName name="A2712240K_Latest">Data1!$Q$36</definedName>
-    <definedName name="A2712242R">Data1!$B$1:$B$10,Data1!$B$11:$B$36</definedName>
-    <definedName name="A2712242R_Data">Data1!$B$11:$B$36</definedName>
-    <definedName name="A2712242R_Latest">Data1!$B$36</definedName>
-    <definedName name="A2712244V">Data1!$J$1:$J$10,Data1!$J$11:$J$36</definedName>
-    <definedName name="A2712244V_Data">Data1!$J$11:$J$36</definedName>
-    <definedName name="A2712244V_Latest">Data1!$J$36</definedName>
-    <definedName name="A2712246X">Data1!$C$1:$C$10,Data1!$C$11:$C$36</definedName>
-    <definedName name="A2712246X_Data">Data1!$C$11:$C$36</definedName>
-    <definedName name="A2712246X_Latest">Data1!$C$36</definedName>
-    <definedName name="A2712248C">Data1!$N$1:$N$10,Data1!$N$11:$N$36</definedName>
-    <definedName name="A2712248C_Data">Data1!$N$11:$N$36</definedName>
-    <definedName name="A2712248C_Latest">Data1!$N$36</definedName>
-    <definedName name="A2712250R">Data1!$O$1:$O$10,Data1!$O$11:$O$36</definedName>
-    <definedName name="A2712250R_Data">Data1!$O$11:$O$36</definedName>
-    <definedName name="A2712250R_Latest">Data1!$O$36</definedName>
-    <definedName name="A2712252V">Data1!$G$1:$G$10,Data1!$G$11:$G$36</definedName>
-    <definedName name="A2712252V_Data">Data1!$G$11:$G$36</definedName>
-    <definedName name="A2712252V_Latest">Data1!$G$36</definedName>
-    <definedName name="A2712254X">Data1!$F$1:$F$10,Data1!$F$11:$F$36</definedName>
-    <definedName name="A2712254X_Data">Data1!$F$11:$F$36</definedName>
-    <definedName name="A2712254X_Latest">Data1!$F$36</definedName>
-    <definedName name="A2712256C">Data1!$S$1:$S$10,Data1!$S$11:$S$36</definedName>
-    <definedName name="A2712256C_Data">Data1!$S$11:$S$36</definedName>
-    <definedName name="A2712256C_Latest">Data1!$S$36</definedName>
-    <definedName name="A2712258J">Data1!$E$1:$E$10,Data1!$E$11:$E$36</definedName>
-    <definedName name="A2712258J_Data">Data1!$E$11:$E$36</definedName>
-    <definedName name="A2712258J_Latest">Data1!$E$36</definedName>
-    <definedName name="A2712260V">Data1!$L$1:$L$10,Data1!$L$11:$L$36</definedName>
-    <definedName name="A2712260V_Data">Data1!$L$11:$L$36</definedName>
-    <definedName name="A2712260V_Latest">Data1!$L$36</definedName>
-    <definedName name="A2712262X">Data1!$T$1:$T$10,Data1!$T$11:$T$36</definedName>
-    <definedName name="A2712262X_Data">Data1!$T$11:$T$36</definedName>
-    <definedName name="A2712262X_Latest">Data1!$T$36</definedName>
-    <definedName name="A2712340V">Data1!$AQ$1:$AQ$10,Data1!$AQ$11:$AQ$36</definedName>
-    <definedName name="A2712340V_Data">Data1!$AQ$11:$AQ$36</definedName>
-    <definedName name="A2712340V_Latest">Data1!$AQ$36</definedName>
-    <definedName name="A2712342X">Data1!$AG$1:$AG$10,Data1!$AG$11:$AG$36</definedName>
-    <definedName name="A2712342X_Data">Data1!$AG$11:$AG$36</definedName>
-    <definedName name="A2712342X_Latest">Data1!$AG$36</definedName>
-    <definedName name="A2712344C">Data1!$AO$1:$AO$10,Data1!$AO$11:$AO$36</definedName>
-    <definedName name="A2712344C_Data">Data1!$AO$11:$AO$36</definedName>
-    <definedName name="A2712344C_Latest">Data1!$AO$36</definedName>
-    <definedName name="A2712346J">Data1!$AJ$1:$AJ$10,Data1!$AJ$11:$AJ$36</definedName>
-    <definedName name="A2712346J_Data">Data1!$AJ$11:$AJ$36</definedName>
-    <definedName name="A2712346J_Latest">Data1!$AJ$36</definedName>
-    <definedName name="A2712348L">Data1!$AH$1:$AH$10,Data1!$AH$11:$AH$36</definedName>
-    <definedName name="A2712348L_Data">Data1!$AH$11:$AH$36</definedName>
-    <definedName name="A2712348L_Latest">Data1!$AH$36</definedName>
-    <definedName name="A2712350X">Data1!$AL$1:$AL$10,Data1!$AL$11:$AL$36</definedName>
-    <definedName name="A2712350X_Data">Data1!$AL$11:$AL$36</definedName>
-    <definedName name="A2712350X_Latest">Data1!$AL$36</definedName>
-    <definedName name="A2712352C">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$36</definedName>
-    <definedName name="A2712352C_Data">Data1!$AC$11:$AC$36</definedName>
-    <definedName name="A2712352C_Latest">Data1!$AC$36</definedName>
-    <definedName name="A2712354J">Data1!$AP$1:$AP$10,Data1!$AP$11:$AP$36</definedName>
-    <definedName name="A2712354J_Data">Data1!$AP$11:$AP$36</definedName>
-    <definedName name="A2712354J_Latest">Data1!$AP$36</definedName>
-    <definedName name="A2712356L">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$36</definedName>
-    <definedName name="A2712356L_Data">Data1!$AA$11:$AA$36</definedName>
-    <definedName name="A2712356L_Latest">Data1!$AA$36</definedName>
-    <definedName name="A2712358T">Data1!$AI$1:$AI$10,Data1!$AI$11:$AI$36</definedName>
-    <definedName name="A2712358T_Data">Data1!$AI$11:$AI$36</definedName>
-    <definedName name="A2712358T_Latest">Data1!$AI$36</definedName>
-    <definedName name="A2712360C">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$36</definedName>
-    <definedName name="A2712360C_Data">Data1!$AB$11:$AB$36</definedName>
-    <definedName name="A2712360C_Latest">Data1!$AB$36</definedName>
-    <definedName name="A2712362J">Data1!$AM$1:$AM$10,Data1!$AM$11:$AM$36</definedName>
-    <definedName name="A2712362J_Data">Data1!$AM$11:$AM$36</definedName>
-    <definedName name="A2712362J_Latest">Data1!$AM$36</definedName>
-    <definedName name="A2712364L">Data1!$AN$1:$AN$10,Data1!$AN$11:$AN$36</definedName>
-    <definedName name="A2712364L_Data">Data1!$AN$11:$AN$36</definedName>
-    <definedName name="A2712364L_Latest">Data1!$AN$36</definedName>
-    <definedName name="A2712366T">Data1!$AF$1:$AF$10,Data1!$AF$11:$AF$36</definedName>
-    <definedName name="A2712366T_Data">Data1!$AF$11:$AF$36</definedName>
-    <definedName name="A2712366T_Latest">Data1!$AF$36</definedName>
-    <definedName name="A2712368W">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$36</definedName>
-    <definedName name="A2712368W_Data">Data1!$AE$11:$AE$36</definedName>
-    <definedName name="A2712368W_Latest">Data1!$AE$36</definedName>
-    <definedName name="A2712370J">Data1!$AR$1:$AR$10,Data1!$AR$11:$AR$36</definedName>
-    <definedName name="A2712370J_Data">Data1!$AR$11:$AR$36</definedName>
-    <definedName name="A2712370J_Latest">Data1!$AR$36</definedName>
-    <definedName name="A2712372L">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$36</definedName>
-    <definedName name="A2712372L_Data">Data1!$AD$11:$AD$36</definedName>
-    <definedName name="A2712372L_Latest">Data1!$AD$36</definedName>
-    <definedName name="A2712374T">Data1!$AK$1:$AK$10,Data1!$AK$11:$AK$36</definedName>
-    <definedName name="A2712374T_Data">Data1!$AK$11:$AK$36</definedName>
-    <definedName name="A2712374T_Latest">Data1!$AK$36</definedName>
-    <definedName name="A2712376W">Data1!$AS$1:$AS$10,Data1!$AS$11:$AS$36</definedName>
-    <definedName name="A2712376W_Data">Data1!$AS$11:$AS$36</definedName>
-    <definedName name="A2712376W_Latest">Data1!$AS$36</definedName>
-    <definedName name="A2712420V">Data1!$X$1:$X$10,Data1!$X$11:$X$36</definedName>
-    <definedName name="A2712420V_Data">Data1!$X$11:$X$36</definedName>
-    <definedName name="A2712420V_Latest">Data1!$X$36</definedName>
-    <definedName name="A2712426J">Data1!$V$1:$V$10,Data1!$V$11:$V$36</definedName>
-    <definedName name="A2712426J_Data">Data1!$V$11:$V$36</definedName>
-    <definedName name="A2712426J_Latest">Data1!$V$36</definedName>
-    <definedName name="A2712428L">Data1!$U$1:$U$10,Data1!$U$11:$U$36</definedName>
-    <definedName name="A2712428L_Data">Data1!$U$11:$U$36</definedName>
-    <definedName name="A2712428L_Latest">Data1!$U$36</definedName>
-    <definedName name="A2712430X">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$36</definedName>
-    <definedName name="A2712430X_Data">Data1!$Y$11:$Y$36</definedName>
-    <definedName name="A2712430X_Latest">Data1!$Y$36</definedName>
-    <definedName name="A2712440C">Data1!$W$1:$W$10,Data1!$W$11:$W$36</definedName>
-    <definedName name="A2712440C_Data">Data1!$W$11:$W$36</definedName>
-    <definedName name="A2712440C_Latest">Data1!$W$36</definedName>
-    <definedName name="A2712452L">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$36</definedName>
-    <definedName name="A2712452L_Data">Data1!$Z$11:$Z$36</definedName>
-    <definedName name="A2712452L_Latest">Data1!$Z$36</definedName>
-    <definedName name="A85019897K">Data1!$BL$1:$BL$10,Data1!$BL$11:$BL$36</definedName>
-    <definedName name="A85019897K_Data">Data1!$BL$11:$BL$36</definedName>
-    <definedName name="A85019897K_Latest">Data1!$BL$36</definedName>
-    <definedName name="A85019899R">Data1!$AT$1:$AT$10,Data1!$AT$11:$AT$36</definedName>
-    <definedName name="A85019899R_Data">Data1!$AT$11:$AT$36</definedName>
-    <definedName name="A85019899R_Latest">Data1!$AT$36</definedName>
-    <definedName name="A85019901R">Data1!$AU$1:$AU$10,Data1!$AU$11:$AU$36</definedName>
-    <definedName name="A85019901R_Data">Data1!$AU$11:$AU$36</definedName>
-    <definedName name="A85019901R_Latest">Data1!$AU$36</definedName>
-    <definedName name="A85019903V">Data1!$AV$1:$AV$10,Data1!$AV$11:$AV$36</definedName>
-    <definedName name="A85019903V_Data">Data1!$AV$11:$AV$36</definedName>
-    <definedName name="A85019903V_Latest">Data1!$AV$36</definedName>
-    <definedName name="A85019905X">Data1!$AW$1:$AW$10,Data1!$AW$11:$AW$36</definedName>
-    <definedName name="A85019905X_Data">Data1!$AW$11:$AW$36</definedName>
-    <definedName name="A85019905X_Latest">Data1!$AW$36</definedName>
-    <definedName name="A85019907C">Data1!$AX$1:$AX$10,Data1!$AX$11:$AX$36</definedName>
-    <definedName name="A85019907C_Data">Data1!$AX$11:$AX$36</definedName>
-    <definedName name="A85019907C_Latest">Data1!$AX$36</definedName>
-    <definedName name="A85019909J">Data1!$AY$1:$AY$10,Data1!$AY$11:$AY$36</definedName>
-    <definedName name="A85019909J_Data">Data1!$AY$11:$AY$36</definedName>
-    <definedName name="A85019909J_Latest">Data1!$AY$36</definedName>
-    <definedName name="A85019911V">Data1!$AZ$1:$AZ$10,Data1!$AZ$11:$AZ$36</definedName>
-    <definedName name="A85019911V_Data">Data1!$AZ$11:$AZ$36</definedName>
-    <definedName name="A85019911V_Latest">Data1!$AZ$36</definedName>
-    <definedName name="A85019913X">Data1!$BA$1:$BA$10,Data1!$BA$11:$BA$36</definedName>
-    <definedName name="A85019913X_Data">Data1!$BA$11:$BA$36</definedName>
-    <definedName name="A85019913X_Latest">Data1!$BA$36</definedName>
-    <definedName name="A85019915C">Data1!$BB$1:$BB$10,Data1!$BB$11:$BB$36</definedName>
-    <definedName name="A85019915C_Data">Data1!$BB$11:$BB$36</definedName>
-    <definedName name="A85019915C_Latest">Data1!$BB$36</definedName>
-    <definedName name="A85019917J">Data1!$BC$1:$BC$10,Data1!$BC$11:$BC$36</definedName>
-    <definedName name="A85019917J_Data">Data1!$BC$11:$BC$36</definedName>
-    <definedName name="A85019917J_Latest">Data1!$BC$36</definedName>
-    <definedName name="A85019919L">Data1!$BD$1:$BD$10,Data1!$BD$11:$BD$36</definedName>
-    <definedName name="A85019919L_Data">Data1!$BD$11:$BD$36</definedName>
-    <definedName name="A85019919L_Latest">Data1!$BD$36</definedName>
-    <definedName name="A85019921X">Data1!$BE$1:$BE$10,Data1!$BE$11:$BE$36</definedName>
-    <definedName name="A85019921X_Data">Data1!$BE$11:$BE$36</definedName>
-    <definedName name="A85019921X_Latest">Data1!$BE$36</definedName>
-    <definedName name="A85019923C">Data1!$BF$1:$BF$10,Data1!$BF$11:$BF$36</definedName>
-    <definedName name="A85019923C_Data">Data1!$BF$11:$BF$36</definedName>
-    <definedName name="A85019923C_Latest">Data1!$BF$36</definedName>
-    <definedName name="A85019925J">Data1!$BG$1:$BG$10,Data1!$BG$11:$BG$36</definedName>
-    <definedName name="A85019925J_Data">Data1!$BG$11:$BG$36</definedName>
-    <definedName name="A85019925J_Latest">Data1!$BG$36</definedName>
-    <definedName name="A85019927L">Data1!$BH$1:$BH$10,Data1!$BH$11:$BH$36</definedName>
-    <definedName name="A85019927L_Data">Data1!$BH$11:$BH$36</definedName>
-    <definedName name="A85019927L_Latest">Data1!$BH$36</definedName>
-    <definedName name="A85019929T">Data1!$BI$1:$BI$10,Data1!$BI$11:$BI$36</definedName>
-    <definedName name="A85019929T_Data">Data1!$BI$11:$BI$36</definedName>
-    <definedName name="A85019929T_Latest">Data1!$BI$36</definedName>
-    <definedName name="A85019931C">Data1!$BJ$1:$BJ$10,Data1!$BJ$11:$BJ$36</definedName>
-    <definedName name="A85019931C_Data">Data1!$BJ$11:$BJ$36</definedName>
-    <definedName name="A85019931C_Latest">Data1!$BJ$36</definedName>
-    <definedName name="A85019933J">Data1!$BK$1:$BK$10,Data1!$BK$11:$BK$36</definedName>
-    <definedName name="A85019933J_Data">Data1!$BK$11:$BK$36</definedName>
-    <definedName name="A85019933J_Latest">Data1!$BK$36</definedName>
-    <definedName name="A85020049T">Data1!$BR$1:$BR$10,Data1!$BR$11:$BR$36</definedName>
-    <definedName name="A85020049T_Data">Data1!$BR$11:$BR$36</definedName>
-    <definedName name="A85020049T_Latest">Data1!$BR$36</definedName>
-    <definedName name="A85020051C">Data1!$BM$1:$BM$10,Data1!$BM$11:$BM$36</definedName>
-    <definedName name="A85020051C_Data">Data1!$BM$11:$BM$36</definedName>
-    <definedName name="A85020051C_Latest">Data1!$BM$36</definedName>
-    <definedName name="A85020053J">Data1!$BN$1:$BN$10,Data1!$BN$11:$BN$36</definedName>
-    <definedName name="A85020053J_Data">Data1!$BN$11:$BN$36</definedName>
-    <definedName name="A85020053J_Latest">Data1!$BN$36</definedName>
-    <definedName name="A85020055L">Data1!$BO$1:$BO$10,Data1!$BO$11:$BO$36</definedName>
-    <definedName name="A85020055L_Data">Data1!$BO$11:$BO$36</definedName>
-    <definedName name="A85020055L_Latest">Data1!$BO$36</definedName>
-    <definedName name="A85020057T">Data1!$BP$1:$BP$10,Data1!$BP$11:$BP$36</definedName>
-    <definedName name="A85020057T_Data">Data1!$BP$11:$BP$36</definedName>
-    <definedName name="A85020057T_Latest">Data1!$BP$36</definedName>
-    <definedName name="A85020059W">Data1!$BQ$1:$BQ$10,Data1!$BQ$11:$BQ$36</definedName>
-    <definedName name="A85020059W_Data">Data1!$BQ$11:$BQ$36</definedName>
-    <definedName name="A85020059W_Latest">Data1!$BQ$36</definedName>
-    <definedName name="A85020629L">Data1!$CK$1:$CK$10,Data1!$CK$11:$CK$36</definedName>
-    <definedName name="A85020629L_Data">Data1!$CK$11:$CK$36</definedName>
-    <definedName name="A85020629L_Latest">Data1!$CK$36</definedName>
-    <definedName name="A85020631X">Data1!$BS$1:$BS$10,Data1!$BS$11:$BS$36</definedName>
-    <definedName name="A85020631X_Data">Data1!$BS$11:$BS$36</definedName>
-    <definedName name="A85020631X_Latest">Data1!$BS$36</definedName>
-    <definedName name="A85020633C">Data1!$BT$1:$BT$10,Data1!$BT$11:$BT$36</definedName>
-    <definedName name="A85020633C_Data">Data1!$BT$11:$BT$36</definedName>
-    <definedName name="A85020633C_Latest">Data1!$BT$36</definedName>
-    <definedName name="A85020635J">Data1!$BU$1:$BU$10,Data1!$BU$11:$BU$36</definedName>
-    <definedName name="A85020635J_Data">Data1!$BU$11:$BU$36</definedName>
-    <definedName name="A85020635J_Latest">Data1!$BU$36</definedName>
-    <definedName name="A85020637L">Data1!$BV$1:$BV$10,Data1!$BV$11:$BV$36</definedName>
-    <definedName name="A85020637L_Data">Data1!$BV$11:$BV$36</definedName>
-    <definedName name="A85020637L_Latest">Data1!$BV$36</definedName>
-    <definedName name="A85020639T">Data1!$BW$1:$BW$10,Data1!$BW$11:$BW$36</definedName>
-    <definedName name="A85020639T_Data">Data1!$BW$11:$BW$36</definedName>
-    <definedName name="A85020639T_Latest">Data1!$BW$36</definedName>
-    <definedName name="A85020641C">Data1!$BX$1:$BX$10,Data1!$BX$11:$BX$36</definedName>
-    <definedName name="A85020641C_Data">Data1!$BX$11:$BX$36</definedName>
-    <definedName name="A85020641C_Latest">Data1!$BX$36</definedName>
-    <definedName name="A85020643J">Data1!$BY$1:$BY$10,Data1!$BY$11:$BY$36</definedName>
-    <definedName name="A85020643J_Data">Data1!$BY$11:$BY$36</definedName>
-    <definedName name="A85020643J_Latest">Data1!$BY$36</definedName>
-    <definedName name="A85020645L">Data1!$BZ$1:$BZ$10,Data1!$BZ$11:$BZ$36</definedName>
-    <definedName name="A85020645L_Data">Data1!$BZ$11:$BZ$36</definedName>
-    <definedName name="A85020645L_Latest">Data1!$BZ$36</definedName>
-    <definedName name="A85020647T">Data1!$CA$1:$CA$10,Data1!$CA$11:$CA$36</definedName>
-    <definedName name="A85020647T_Data">Data1!$CA$11:$CA$36</definedName>
-    <definedName name="A85020647T_Latest">Data1!$CA$36</definedName>
-    <definedName name="A85020649W">Data1!$CB$1:$CB$10,Data1!$CB$11:$CB$36</definedName>
-    <definedName name="A85020649W_Data">Data1!$CB$11:$CB$36</definedName>
-    <definedName name="A85020649W_Latest">Data1!$CB$36</definedName>
-    <definedName name="A85020651J">Data1!$CC$1:$CC$10,Data1!$CC$11:$CC$36</definedName>
-    <definedName name="A85020651J_Data">Data1!$CC$11:$CC$36</definedName>
-    <definedName name="A85020651J_Latest">Data1!$CC$36</definedName>
-    <definedName name="A85020653L">Data1!$CD$1:$CD$10,Data1!$CD$11:$CD$36</definedName>
-    <definedName name="A85020653L_Data">Data1!$CD$11:$CD$36</definedName>
-    <definedName name="A85020653L_Latest">Data1!$CD$36</definedName>
-    <definedName name="A85020655T">Data1!$CE$1:$CE$10,Data1!$CE$11:$CE$36</definedName>
-    <definedName name="A85020655T_Data">Data1!$CE$11:$CE$36</definedName>
-    <definedName name="A85020655T_Latest">Data1!$CE$36</definedName>
-    <definedName name="A85020657W">Data1!$CF$1:$CF$10,Data1!$CF$11:$CF$36</definedName>
-    <definedName name="A85020657W_Data">Data1!$CF$11:$CF$36</definedName>
-    <definedName name="A85020657W_Latest">Data1!$CF$36</definedName>
-    <definedName name="A85020659A">Data1!$CG$1:$CG$10,Data1!$CG$11:$CG$36</definedName>
-    <definedName name="A85020659A_Data">Data1!$CG$11:$CG$36</definedName>
-    <definedName name="A85020659A_Latest">Data1!$CG$36</definedName>
-    <definedName name="A85020661L">Data1!$CH$1:$CH$10,Data1!$CH$11:$CH$36</definedName>
-    <definedName name="A85020661L_Data">Data1!$CH$11:$CH$36</definedName>
-    <definedName name="A85020661L_Latest">Data1!$CH$36</definedName>
-    <definedName name="A85020663T">Data1!$CI$1:$CI$10,Data1!$CI$11:$CI$36</definedName>
-    <definedName name="A85020663T_Data">Data1!$CI$11:$CI$36</definedName>
-    <definedName name="A85020663T_Latest">Data1!$CI$36</definedName>
-    <definedName name="A85020665W">Data1!$CJ$1:$CJ$10,Data1!$CJ$11:$CJ$36</definedName>
-    <definedName name="A85020665W_Data">Data1!$CJ$11:$CJ$36</definedName>
-    <definedName name="A85020665W_Latest">Data1!$CJ$36</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$36</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$36</definedName>
+    <definedName name="A2712226R">Data1!$R$1:$R$10,Data1!$R$11:$R$38</definedName>
+    <definedName name="A2712226R_Data">Data1!$R$11:$R$38</definedName>
+    <definedName name="A2712226R_Latest">Data1!$R$38</definedName>
+    <definedName name="A2712228V">Data1!$H$1:$H$10,Data1!$H$11:$H$38</definedName>
+    <definedName name="A2712228V_Data">Data1!$H$11:$H$38</definedName>
+    <definedName name="A2712228V_Latest">Data1!$H$38</definedName>
+    <definedName name="A2712230F">Data1!$P$1:$P$10,Data1!$P$11:$P$38</definedName>
+    <definedName name="A2712230F_Data">Data1!$P$11:$P$38</definedName>
+    <definedName name="A2712230F_Latest">Data1!$P$38</definedName>
+    <definedName name="A2712232K">Data1!$K$1:$K$10,Data1!$K$11:$K$38</definedName>
+    <definedName name="A2712232K_Data">Data1!$K$11:$K$38</definedName>
+    <definedName name="A2712232K_Latest">Data1!$K$38</definedName>
+    <definedName name="A2712234R">Data1!$I$1:$I$10,Data1!$I$11:$I$38</definedName>
+    <definedName name="A2712234R_Data">Data1!$I$11:$I$38</definedName>
+    <definedName name="A2712234R_Latest">Data1!$I$38</definedName>
+    <definedName name="A2712236V">Data1!$M$1:$M$10,Data1!$M$11:$M$38</definedName>
+    <definedName name="A2712236V_Data">Data1!$M$11:$M$38</definedName>
+    <definedName name="A2712236V_Latest">Data1!$M$38</definedName>
+    <definedName name="A2712238X">Data1!$D$1:$D$10,Data1!$D$11:$D$38</definedName>
+    <definedName name="A2712238X_Data">Data1!$D$11:$D$38</definedName>
+    <definedName name="A2712238X_Latest">Data1!$D$38</definedName>
+    <definedName name="A2712240K">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$38</definedName>
+    <definedName name="A2712240K_Data">Data1!$Q$11:$Q$38</definedName>
+    <definedName name="A2712240K_Latest">Data1!$Q$38</definedName>
+    <definedName name="A2712242R">Data1!$B$1:$B$10,Data1!$B$11:$B$38</definedName>
+    <definedName name="A2712242R_Data">Data1!$B$11:$B$38</definedName>
+    <definedName name="A2712242R_Latest">Data1!$B$38</definedName>
+    <definedName name="A2712244V">Data1!$J$1:$J$10,Data1!$J$11:$J$38</definedName>
+    <definedName name="A2712244V_Data">Data1!$J$11:$J$38</definedName>
+    <definedName name="A2712244V_Latest">Data1!$J$38</definedName>
+    <definedName name="A2712246X">Data1!$C$1:$C$10,Data1!$C$11:$C$38</definedName>
+    <definedName name="A2712246X_Data">Data1!$C$11:$C$38</definedName>
+    <definedName name="A2712246X_Latest">Data1!$C$38</definedName>
+    <definedName name="A2712248C">Data1!$N$1:$N$10,Data1!$N$11:$N$38</definedName>
+    <definedName name="A2712248C_Data">Data1!$N$11:$N$38</definedName>
+    <definedName name="A2712248C_Latest">Data1!$N$38</definedName>
+    <definedName name="A2712250R">Data1!$O$1:$O$10,Data1!$O$11:$O$38</definedName>
+    <definedName name="A2712250R_Data">Data1!$O$11:$O$38</definedName>
+    <definedName name="A2712250R_Latest">Data1!$O$38</definedName>
+    <definedName name="A2712252V">Data1!$G$1:$G$10,Data1!$G$11:$G$38</definedName>
+    <definedName name="A2712252V_Data">Data1!$G$11:$G$38</definedName>
+    <definedName name="A2712252V_Latest">Data1!$G$38</definedName>
+    <definedName name="A2712254X">Data1!$F$1:$F$10,Data1!$F$11:$F$38</definedName>
+    <definedName name="A2712254X_Data">Data1!$F$11:$F$38</definedName>
+    <definedName name="A2712254X_Latest">Data1!$F$38</definedName>
+    <definedName name="A2712256C">Data1!$S$1:$S$10,Data1!$S$11:$S$38</definedName>
+    <definedName name="A2712256C_Data">Data1!$S$11:$S$38</definedName>
+    <definedName name="A2712256C_Latest">Data1!$S$38</definedName>
+    <definedName name="A2712258J">Data1!$E$1:$E$10,Data1!$E$11:$E$38</definedName>
+    <definedName name="A2712258J_Data">Data1!$E$11:$E$38</definedName>
+    <definedName name="A2712258J_Latest">Data1!$E$38</definedName>
+    <definedName name="A2712260V">Data1!$L$1:$L$10,Data1!$L$11:$L$38</definedName>
+    <definedName name="A2712260V_Data">Data1!$L$11:$L$38</definedName>
+    <definedName name="A2712260V_Latest">Data1!$L$38</definedName>
+    <definedName name="A2712262X">Data1!$T$1:$T$10,Data1!$T$11:$T$38</definedName>
+    <definedName name="A2712262X_Data">Data1!$T$11:$T$38</definedName>
+    <definedName name="A2712262X_Latest">Data1!$T$38</definedName>
+    <definedName name="A2712340V">Data1!$AQ$1:$AQ$10,Data1!$AQ$11:$AQ$38</definedName>
+    <definedName name="A2712340V_Data">Data1!$AQ$11:$AQ$38</definedName>
+    <definedName name="A2712340V_Latest">Data1!$AQ$38</definedName>
+    <definedName name="A2712342X">Data1!$AG$1:$AG$10,Data1!$AG$11:$AG$38</definedName>
+    <definedName name="A2712342X_Data">Data1!$AG$11:$AG$38</definedName>
+    <definedName name="A2712342X_Latest">Data1!$AG$38</definedName>
+    <definedName name="A2712344C">Data1!$AO$1:$AO$10,Data1!$AO$11:$AO$38</definedName>
+    <definedName name="A2712344C_Data">Data1!$AO$11:$AO$38</definedName>
+    <definedName name="A2712344C_Latest">Data1!$AO$38</definedName>
+    <definedName name="A2712346J">Data1!$AJ$1:$AJ$10,Data1!$AJ$11:$AJ$38</definedName>
+    <definedName name="A2712346J_Data">Data1!$AJ$11:$AJ$38</definedName>
+    <definedName name="A2712346J_Latest">Data1!$AJ$38</definedName>
+    <definedName name="A2712348L">Data1!$AH$1:$AH$10,Data1!$AH$11:$AH$38</definedName>
+    <definedName name="A2712348L_Data">Data1!$AH$11:$AH$38</definedName>
+    <definedName name="A2712348L_Latest">Data1!$AH$38</definedName>
+    <definedName name="A2712350X">Data1!$AL$1:$AL$10,Data1!$AL$11:$AL$38</definedName>
+    <definedName name="A2712350X_Data">Data1!$AL$11:$AL$38</definedName>
+    <definedName name="A2712350X_Latest">Data1!$AL$38</definedName>
+    <definedName name="A2712352C">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$38</definedName>
+    <definedName name="A2712352C_Data">Data1!$AC$11:$AC$38</definedName>
+    <definedName name="A2712352C_Latest">Data1!$AC$38</definedName>
+    <definedName name="A2712354J">Data1!$AP$1:$AP$10,Data1!$AP$11:$AP$38</definedName>
+    <definedName name="A2712354J_Data">Data1!$AP$11:$AP$38</definedName>
+    <definedName name="A2712354J_Latest">Data1!$AP$38</definedName>
+    <definedName name="A2712356L">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$38</definedName>
+    <definedName name="A2712356L_Data">Data1!$AA$11:$AA$38</definedName>
+    <definedName name="A2712356L_Latest">Data1!$AA$38</definedName>
+    <definedName name="A2712358T">Data1!$AI$1:$AI$10,Data1!$AI$11:$AI$38</definedName>
+    <definedName name="A2712358T_Data">Data1!$AI$11:$AI$38</definedName>
+    <definedName name="A2712358T_Latest">Data1!$AI$38</definedName>
+    <definedName name="A2712360C">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$38</definedName>
+    <definedName name="A2712360C_Data">Data1!$AB$11:$AB$38</definedName>
+    <definedName name="A2712360C_Latest">Data1!$AB$38</definedName>
+    <definedName name="A2712362J">Data1!$AM$1:$AM$10,Data1!$AM$11:$AM$38</definedName>
+    <definedName name="A2712362J_Data">Data1!$AM$11:$AM$38</definedName>
+    <definedName name="A2712362J_Latest">Data1!$AM$38</definedName>
+    <definedName name="A2712364L">Data1!$AN$1:$AN$10,Data1!$AN$11:$AN$38</definedName>
+    <definedName name="A2712364L_Data">Data1!$AN$11:$AN$38</definedName>
+    <definedName name="A2712364L_Latest">Data1!$AN$38</definedName>
+    <definedName name="A2712366T">Data1!$AF$1:$AF$10,Data1!$AF$11:$AF$38</definedName>
+    <definedName name="A2712366T_Data">Data1!$AF$11:$AF$38</definedName>
+    <definedName name="A2712366T_Latest">Data1!$AF$38</definedName>
+    <definedName name="A2712368W">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$38</definedName>
+    <definedName name="A2712368W_Data">Data1!$AE$11:$AE$38</definedName>
+    <definedName name="A2712368W_Latest">Data1!$AE$38</definedName>
+    <definedName name="A2712370J">Data1!$AR$1:$AR$10,Data1!$AR$11:$AR$38</definedName>
+    <definedName name="A2712370J_Data">Data1!$AR$11:$AR$38</definedName>
+    <definedName name="A2712370J_Latest">Data1!$AR$38</definedName>
+    <definedName name="A2712372L">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$38</definedName>
+    <definedName name="A2712372L_Data">Data1!$AD$11:$AD$38</definedName>
+    <definedName name="A2712372L_Latest">Data1!$AD$38</definedName>
+    <definedName name="A2712374T">Data1!$AK$1:$AK$10,Data1!$AK$11:$AK$38</definedName>
+    <definedName name="A2712374T_Data">Data1!$AK$11:$AK$38</definedName>
+    <definedName name="A2712374T_Latest">Data1!$AK$38</definedName>
+    <definedName name="A2712376W">Data1!$AS$1:$AS$10,Data1!$AS$11:$AS$38</definedName>
+    <definedName name="A2712376W_Data">Data1!$AS$11:$AS$38</definedName>
+    <definedName name="A2712376W_Latest">Data1!$AS$38</definedName>
+    <definedName name="A2712420V">Data1!$X$1:$X$10,Data1!$X$11:$X$38</definedName>
+    <definedName name="A2712420V_Data">Data1!$X$11:$X$38</definedName>
+    <definedName name="A2712420V_Latest">Data1!$X$38</definedName>
+    <definedName name="A2712426J">Data1!$V$1:$V$10,Data1!$V$11:$V$38</definedName>
+    <definedName name="A2712426J_Data">Data1!$V$11:$V$38</definedName>
+    <definedName name="A2712426J_Latest">Data1!$V$38</definedName>
+    <definedName name="A2712428L">Data1!$U$1:$U$10,Data1!$U$11:$U$38</definedName>
+    <definedName name="A2712428L_Data">Data1!$U$11:$U$38</definedName>
+    <definedName name="A2712428L_Latest">Data1!$U$38</definedName>
+    <definedName name="A2712430X">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$38</definedName>
+    <definedName name="A2712430X_Data">Data1!$Y$11:$Y$38</definedName>
+    <definedName name="A2712430X_Latest">Data1!$Y$38</definedName>
+    <definedName name="A2712440C">Data1!$W$1:$W$10,Data1!$W$11:$W$38</definedName>
+    <definedName name="A2712440C_Data">Data1!$W$11:$W$38</definedName>
+    <definedName name="A2712440C_Latest">Data1!$W$38</definedName>
+    <definedName name="A2712452L">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$38</definedName>
+    <definedName name="A2712452L_Data">Data1!$Z$11:$Z$38</definedName>
+    <definedName name="A2712452L_Latest">Data1!$Z$38</definedName>
+    <definedName name="A85019897K">Data1!$BL$1:$BL$10,Data1!$BL$11:$BL$38</definedName>
+    <definedName name="A85019897K_Data">Data1!$BL$11:$BL$38</definedName>
+    <definedName name="A85019897K_Latest">Data1!$BL$38</definedName>
+    <definedName name="A85019899R">Data1!$AT$1:$AT$10,Data1!$AT$11:$AT$38</definedName>
+    <definedName name="A85019899R_Data">Data1!$AT$11:$AT$38</definedName>
+    <definedName name="A85019899R_Latest">Data1!$AT$38</definedName>
+    <definedName name="A85019901R">Data1!$AU$1:$AU$10,Data1!$AU$11:$AU$38</definedName>
+    <definedName name="A85019901R_Data">Data1!$AU$11:$AU$38</definedName>
+    <definedName name="A85019901R_Latest">Data1!$AU$38</definedName>
+    <definedName name="A85019903V">Data1!$AV$1:$AV$10,Data1!$AV$11:$AV$38</definedName>
+    <definedName name="A85019903V_Data">Data1!$AV$11:$AV$38</definedName>
+    <definedName name="A85019903V_Latest">Data1!$AV$38</definedName>
+    <definedName name="A85019905X">Data1!$AW$1:$AW$10,Data1!$AW$11:$AW$38</definedName>
+    <definedName name="A85019905X_Data">Data1!$AW$11:$AW$38</definedName>
+    <definedName name="A85019905X_Latest">Data1!$AW$38</definedName>
+    <definedName name="A85019907C">Data1!$AX$1:$AX$10,Data1!$AX$11:$AX$38</definedName>
+    <definedName name="A85019907C_Data">Data1!$AX$11:$AX$38</definedName>
+    <definedName name="A85019907C_Latest">Data1!$AX$38</definedName>
+    <definedName name="A85019909J">Data1!$AY$1:$AY$10,Data1!$AY$11:$AY$38</definedName>
+    <definedName name="A85019909J_Data">Data1!$AY$11:$AY$38</definedName>
+    <definedName name="A85019909J_Latest">Data1!$AY$38</definedName>
+    <definedName name="A85019911V">Data1!$AZ$1:$AZ$10,Data1!$AZ$11:$AZ$38</definedName>
+    <definedName name="A85019911V_Data">Data1!$AZ$11:$AZ$38</definedName>
+    <definedName name="A85019911V_Latest">Data1!$AZ$38</definedName>
+    <definedName name="A85019913X">Data1!$BA$1:$BA$10,Data1!$BA$11:$BA$38</definedName>
+    <definedName name="A85019913X_Data">Data1!$BA$11:$BA$38</definedName>
+    <definedName name="A85019913X_Latest">Data1!$BA$38</definedName>
+    <definedName name="A85019915C">Data1!$BB$1:$BB$10,Data1!$BB$11:$BB$38</definedName>
+    <definedName name="A85019915C_Data">Data1!$BB$11:$BB$38</definedName>
+    <definedName name="A85019915C_Latest">Data1!$BB$38</definedName>
+    <definedName name="A85019917J">Data1!$BC$1:$BC$10,Data1!$BC$11:$BC$38</definedName>
+    <definedName name="A85019917J_Data">Data1!$BC$11:$BC$38</definedName>
+    <definedName name="A85019917J_Latest">Data1!$BC$38</definedName>
+    <definedName name="A85019919L">Data1!$BD$1:$BD$10,Data1!$BD$11:$BD$38</definedName>
+    <definedName name="A85019919L_Data">Data1!$BD$11:$BD$38</definedName>
+    <definedName name="A85019919L_Latest">Data1!$BD$38</definedName>
+    <definedName name="A85019921X">Data1!$BE$1:$BE$10,Data1!$BE$11:$BE$38</definedName>
+    <definedName name="A85019921X_Data">Data1!$BE$11:$BE$38</definedName>
+    <definedName name="A85019921X_Latest">Data1!$BE$38</definedName>
+    <definedName name="A85019923C">Data1!$BF$1:$BF$10,Data1!$BF$11:$BF$38</definedName>
+    <definedName name="A85019923C_Data">Data1!$BF$11:$BF$38</definedName>
+    <definedName name="A85019923C_Latest">Data1!$BF$38</definedName>
+    <definedName name="A85019925J">Data1!$BG$1:$BG$10,Data1!$BG$11:$BG$38</definedName>
+    <definedName name="A85019925J_Data">Data1!$BG$11:$BG$38</definedName>
+    <definedName name="A85019925J_Latest">Data1!$BG$38</definedName>
+    <definedName name="A85019927L">Data1!$BH$1:$BH$10,Data1!$BH$11:$BH$38</definedName>
+    <definedName name="A85019927L_Data">Data1!$BH$11:$BH$38</definedName>
+    <definedName name="A85019927L_Latest">Data1!$BH$38</definedName>
+    <definedName name="A85019929T">Data1!$BI$1:$BI$10,Data1!$BI$11:$BI$38</definedName>
+    <definedName name="A85019929T_Data">Data1!$BI$11:$BI$38</definedName>
+    <definedName name="A85019929T_Latest">Data1!$BI$38</definedName>
+    <definedName name="A85019931C">Data1!$BJ$1:$BJ$10,Data1!$BJ$11:$BJ$38</definedName>
+    <definedName name="A85019931C_Data">Data1!$BJ$11:$BJ$38</definedName>
+    <definedName name="A85019931C_Latest">Data1!$BJ$38</definedName>
+    <definedName name="A85019933J">Data1!$BK$1:$BK$10,Data1!$BK$11:$BK$38</definedName>
+    <definedName name="A85019933J_Data">Data1!$BK$11:$BK$38</definedName>
+    <definedName name="A85019933J_Latest">Data1!$BK$38</definedName>
+    <definedName name="A85020049T">Data1!$BR$1:$BR$10,Data1!$BR$11:$BR$38</definedName>
+    <definedName name="A85020049T_Data">Data1!$BR$11:$BR$38</definedName>
+    <definedName name="A85020049T_Latest">Data1!$BR$38</definedName>
+    <definedName name="A85020051C">Data1!$BM$1:$BM$10,Data1!$BM$11:$BM$38</definedName>
+    <definedName name="A85020051C_Data">Data1!$BM$11:$BM$38</definedName>
+    <definedName name="A85020051C_Latest">Data1!$BM$38</definedName>
+    <definedName name="A85020053J">Data1!$BN$1:$BN$10,Data1!$BN$11:$BN$38</definedName>
+    <definedName name="A85020053J_Data">Data1!$BN$11:$BN$38</definedName>
+    <definedName name="A85020053J_Latest">Data1!$BN$38</definedName>
+    <definedName name="A85020055L">Data1!$BO$1:$BO$10,Data1!$BO$11:$BO$38</definedName>
+    <definedName name="A85020055L_Data">Data1!$BO$11:$BO$38</definedName>
+    <definedName name="A85020055L_Latest">Data1!$BO$38</definedName>
+    <definedName name="A85020057T">Data1!$BP$1:$BP$10,Data1!$BP$11:$BP$38</definedName>
+    <definedName name="A85020057T_Data">Data1!$BP$11:$BP$38</definedName>
+    <definedName name="A85020057T_Latest">Data1!$BP$38</definedName>
+    <definedName name="A85020059W">Data1!$BQ$1:$BQ$10,Data1!$BQ$11:$BQ$38</definedName>
+    <definedName name="A85020059W_Data">Data1!$BQ$11:$BQ$38</definedName>
+    <definedName name="A85020059W_Latest">Data1!$BQ$38</definedName>
+    <definedName name="A85020629L">Data1!$CK$1:$CK$10,Data1!$CK$11:$CK$38</definedName>
+    <definedName name="A85020629L_Data">Data1!$CK$11:$CK$38</definedName>
+    <definedName name="A85020629L_Latest">Data1!$CK$38</definedName>
+    <definedName name="A85020631X">Data1!$BS$1:$BS$10,Data1!$BS$11:$BS$38</definedName>
+    <definedName name="A85020631X_Data">Data1!$BS$11:$BS$38</definedName>
+    <definedName name="A85020631X_Latest">Data1!$BS$38</definedName>
+    <definedName name="A85020633C">Data1!$BT$1:$BT$10,Data1!$BT$11:$BT$38</definedName>
+    <definedName name="A85020633C_Data">Data1!$BT$11:$BT$38</definedName>
+    <definedName name="A85020633C_Latest">Data1!$BT$38</definedName>
+    <definedName name="A85020635J">Data1!$BU$1:$BU$10,Data1!$BU$11:$BU$38</definedName>
+    <definedName name="A85020635J_Data">Data1!$BU$11:$BU$38</definedName>
+    <definedName name="A85020635J_Latest">Data1!$BU$38</definedName>
+    <definedName name="A85020637L">Data1!$BV$1:$BV$10,Data1!$BV$11:$BV$38</definedName>
+    <definedName name="A85020637L_Data">Data1!$BV$11:$BV$38</definedName>
+    <definedName name="A85020637L_Latest">Data1!$BV$38</definedName>
+    <definedName name="A85020639T">Data1!$BW$1:$BW$10,Data1!$BW$11:$BW$38</definedName>
+    <definedName name="A85020639T_Data">Data1!$BW$11:$BW$38</definedName>
+    <definedName name="A85020639T_Latest">Data1!$BW$38</definedName>
+    <definedName name="A85020641C">Data1!$BX$1:$BX$10,Data1!$BX$11:$BX$38</definedName>
+    <definedName name="A85020641C_Data">Data1!$BX$11:$BX$38</definedName>
+    <definedName name="A85020641C_Latest">Data1!$BX$38</definedName>
+    <definedName name="A85020643J">Data1!$BY$1:$BY$10,Data1!$BY$11:$BY$38</definedName>
+    <definedName name="A85020643J_Data">Data1!$BY$11:$BY$38</definedName>
+    <definedName name="A85020643J_Latest">Data1!$BY$38</definedName>
+    <definedName name="A85020645L">Data1!$BZ$1:$BZ$10,Data1!$BZ$11:$BZ$38</definedName>
+    <definedName name="A85020645L_Data">Data1!$BZ$11:$BZ$38</definedName>
+    <definedName name="A85020645L_Latest">Data1!$BZ$38</definedName>
+    <definedName name="A85020647T">Data1!$CA$1:$CA$10,Data1!$CA$11:$CA$38</definedName>
+    <definedName name="A85020647T_Data">Data1!$CA$11:$CA$38</definedName>
+    <definedName name="A85020647T_Latest">Data1!$CA$38</definedName>
+    <definedName name="A85020649W">Data1!$CB$1:$CB$10,Data1!$CB$11:$CB$38</definedName>
+    <definedName name="A85020649W_Data">Data1!$CB$11:$CB$38</definedName>
+    <definedName name="A85020649W_Latest">Data1!$CB$38</definedName>
+    <definedName name="A85020651J">Data1!$CC$1:$CC$10,Data1!$CC$11:$CC$38</definedName>
+    <definedName name="A85020651J_Data">Data1!$CC$11:$CC$38</definedName>
+    <definedName name="A85020651J_Latest">Data1!$CC$38</definedName>
+    <definedName name="A85020653L">Data1!$CD$1:$CD$10,Data1!$CD$11:$CD$38</definedName>
+    <definedName name="A85020653L_Data">Data1!$CD$11:$CD$38</definedName>
+    <definedName name="A85020653L_Latest">Data1!$CD$38</definedName>
+    <definedName name="A85020655T">Data1!$CE$1:$CE$10,Data1!$CE$11:$CE$38</definedName>
+    <definedName name="A85020655T_Data">Data1!$CE$11:$CE$38</definedName>
+    <definedName name="A85020655T_Latest">Data1!$CE$38</definedName>
+    <definedName name="A85020657W">Data1!$CF$1:$CF$10,Data1!$CF$11:$CF$38</definedName>
+    <definedName name="A85020657W_Data">Data1!$CF$11:$CF$38</definedName>
+    <definedName name="A85020657W_Latest">Data1!$CF$38</definedName>
+    <definedName name="A85020659A">Data1!$CG$1:$CG$10,Data1!$CG$11:$CG$38</definedName>
+    <definedName name="A85020659A_Data">Data1!$CG$11:$CG$38</definedName>
+    <definedName name="A85020659A_Latest">Data1!$CG$38</definedName>
+    <definedName name="A85020661L">Data1!$CH$1:$CH$10,Data1!$CH$11:$CH$38</definedName>
+    <definedName name="A85020661L_Data">Data1!$CH$11:$CH$38</definedName>
+    <definedName name="A85020661L_Latest">Data1!$CH$38</definedName>
+    <definedName name="A85020663T">Data1!$CI$1:$CI$10,Data1!$CI$11:$CI$38</definedName>
+    <definedName name="A85020663T_Data">Data1!$CI$11:$CI$38</definedName>
+    <definedName name="A85020663T_Latest">Data1!$CI$38</definedName>
+    <definedName name="A85020665W">Data1!$CJ$1:$CJ$10,Data1!$CJ$11:$CJ$38</definedName>
+    <definedName name="A85020665W_Data">Data1!$CJ$11:$CJ$38</definedName>
+    <definedName name="A85020665W_Latest">Data1!$CJ$38</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$38</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$38</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -3892,7 +3892,7 @@
     <t>Freq.</t>
   </si>
   <si>
-    <t>© Commonwealth of Australia  2023</t>
+    <t>© Commonwealth of Australia  2026</t>
   </si>
 </sst>
 </file>
@@ -4573,10 +4573,10 @@
         <v>35947</v>
       </c>
       <c r="G12" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H12" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>97</v>
@@ -4605,10 +4605,10 @@
         <v>35947</v>
       </c>
       <c r="G13" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H13" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>97</v>
@@ -4637,10 +4637,10 @@
         <v>35947</v>
       </c>
       <c r="G14" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H14" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>97</v>
@@ -4669,10 +4669,10 @@
         <v>35947</v>
       </c>
       <c r="G15" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H15" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>97</v>
@@ -4701,10 +4701,10 @@
         <v>35947</v>
       </c>
       <c r="G16" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H16" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>97</v>
@@ -4733,10 +4733,10 @@
         <v>35947</v>
       </c>
       <c r="G17" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H17" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>97</v>
@@ -4765,10 +4765,10 @@
         <v>35947</v>
       </c>
       <c r="G18" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H18" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>97</v>
@@ -4797,10 +4797,10 @@
         <v>35947</v>
       </c>
       <c r="G19" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H19" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>97</v>
@@ -4829,10 +4829,10 @@
         <v>35947</v>
       </c>
       <c r="G20" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H20" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>97</v>
@@ -4861,10 +4861,10 @@
         <v>35947</v>
       </c>
       <c r="G21" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H21" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>97</v>
@@ -4893,10 +4893,10 @@
         <v>35947</v>
       </c>
       <c r="G22" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H22" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>97</v>
@@ -4925,10 +4925,10 @@
         <v>35947</v>
       </c>
       <c r="G23" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H23" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>97</v>
@@ -4957,10 +4957,10 @@
         <v>35947</v>
       </c>
       <c r="G24" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H24" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>97</v>
@@ -4989,10 +4989,10 @@
         <v>35947</v>
       </c>
       <c r="G25" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H25" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>97</v>
@@ -5021,10 +5021,10 @@
         <v>35947</v>
       </c>
       <c r="G26" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H26" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>97</v>
@@ -5053,10 +5053,10 @@
         <v>35947</v>
       </c>
       <c r="G27" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H27" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>97</v>
@@ -5085,10 +5085,10 @@
         <v>35947</v>
       </c>
       <c r="G28" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H28" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>97</v>
@@ -5117,10 +5117,10 @@
         <v>35947</v>
       </c>
       <c r="G29" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H29" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>97</v>
@@ -5149,10 +5149,10 @@
         <v>35947</v>
       </c>
       <c r="G30" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H30" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>97</v>
@@ -5181,10 +5181,10 @@
         <v>35947</v>
       </c>
       <c r="G31" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H31" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>97</v>
@@ -5213,10 +5213,10 @@
         <v>35947</v>
       </c>
       <c r="G32" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H32" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>97</v>
@@ -5245,10 +5245,10 @@
         <v>35947</v>
       </c>
       <c r="G33" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H33" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>97</v>
@@ -5277,10 +5277,10 @@
         <v>35947</v>
       </c>
       <c r="G34" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H34" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>97</v>
@@ -5309,10 +5309,10 @@
         <v>35947</v>
       </c>
       <c r="G35" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H35" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>97</v>
@@ -5341,10 +5341,10 @@
         <v>35947</v>
       </c>
       <c r="G36" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H36" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>97</v>
@@ -5373,10 +5373,10 @@
         <v>35947</v>
       </c>
       <c r="G37" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H37" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>97</v>
@@ -5405,10 +5405,10 @@
         <v>35947</v>
       </c>
       <c r="G38" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H38" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>97</v>
@@ -5437,10 +5437,10 @@
         <v>35947</v>
       </c>
       <c r="G39" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H39" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I39" s="10" t="s">
         <v>97</v>
@@ -5469,10 +5469,10 @@
         <v>35947</v>
       </c>
       <c r="G40" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H40" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I40" s="10" t="s">
         <v>97</v>
@@ -5501,10 +5501,10 @@
         <v>35947</v>
       </c>
       <c r="G41" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H41" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I41" s="10" t="s">
         <v>97</v>
@@ -5533,10 +5533,10 @@
         <v>35947</v>
       </c>
       <c r="G42" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H42" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I42" s="10" t="s">
         <v>97</v>
@@ -5565,10 +5565,10 @@
         <v>35947</v>
       </c>
       <c r="G43" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H43" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>97</v>
@@ -5597,10 +5597,10 @@
         <v>35947</v>
       </c>
       <c r="G44" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H44" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>97</v>
@@ -5629,10 +5629,10 @@
         <v>35947</v>
       </c>
       <c r="G45" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H45" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I45" s="10" t="s">
         <v>97</v>
@@ -5661,10 +5661,10 @@
         <v>35947</v>
       </c>
       <c r="G46" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H46" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I46" s="10" t="s">
         <v>97</v>
@@ -5693,10 +5693,10 @@
         <v>35947</v>
       </c>
       <c r="G47" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H47" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I47" s="10" t="s">
         <v>97</v>
@@ -5725,10 +5725,10 @@
         <v>35947</v>
       </c>
       <c r="G48" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H48" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>97</v>
@@ -5757,10 +5757,10 @@
         <v>35947</v>
       </c>
       <c r="G49" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H49" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I49" s="10" t="s">
         <v>97</v>
@@ -5789,10 +5789,10 @@
         <v>35947</v>
       </c>
       <c r="G50" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H50" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I50" s="10" t="s">
         <v>97</v>
@@ -5821,10 +5821,10 @@
         <v>35947</v>
       </c>
       <c r="G51" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H51" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I51" s="10" t="s">
         <v>97</v>
@@ -5853,10 +5853,10 @@
         <v>35947</v>
       </c>
       <c r="G52" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H52" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I52" s="10" t="s">
         <v>97</v>
@@ -5885,10 +5885,10 @@
         <v>35947</v>
       </c>
       <c r="G53" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H53" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I53" s="10" t="s">
         <v>97</v>
@@ -5917,10 +5917,10 @@
         <v>35947</v>
       </c>
       <c r="G54" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H54" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I54" s="10" t="s">
         <v>97</v>
@@ -5949,10 +5949,10 @@
         <v>35947</v>
       </c>
       <c r="G55" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H55" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I55" s="10" t="s">
         <v>97</v>
@@ -5981,10 +5981,10 @@
         <v>35947</v>
       </c>
       <c r="G56" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H56" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I56" s="10" t="s">
         <v>145</v>
@@ -6013,10 +6013,10 @@
         <v>35947</v>
       </c>
       <c r="G57" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H57" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I57" s="10" t="s">
         <v>145</v>
@@ -6045,10 +6045,10 @@
         <v>35947</v>
       </c>
       <c r="G58" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H58" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I58" s="10" t="s">
         <v>145</v>
@@ -6077,10 +6077,10 @@
         <v>35947</v>
       </c>
       <c r="G59" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H59" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I59" s="10" t="s">
         <v>145</v>
@@ -6109,10 +6109,10 @@
         <v>35947</v>
       </c>
       <c r="G60" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H60" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I60" s="10" t="s">
         <v>145</v>
@@ -6141,10 +6141,10 @@
         <v>35947</v>
       </c>
       <c r="G61" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H61" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I61" s="10" t="s">
         <v>145</v>
@@ -6173,10 +6173,10 @@
         <v>35947</v>
       </c>
       <c r="G62" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H62" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I62" s="10" t="s">
         <v>145</v>
@@ -6205,10 +6205,10 @@
         <v>35947</v>
       </c>
       <c r="G63" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H63" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I63" s="10" t="s">
         <v>145</v>
@@ -6237,10 +6237,10 @@
         <v>35947</v>
       </c>
       <c r="G64" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H64" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I64" s="10" t="s">
         <v>145</v>
@@ -6269,10 +6269,10 @@
         <v>35947</v>
       </c>
       <c r="G65" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H65" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I65" s="10" t="s">
         <v>145</v>
@@ -6301,10 +6301,10 @@
         <v>35947</v>
       </c>
       <c r="G66" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H66" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I66" s="10" t="s">
         <v>145</v>
@@ -6333,10 +6333,10 @@
         <v>35947</v>
       </c>
       <c r="G67" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H67" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I67" s="10" t="s">
         <v>145</v>
@@ -6365,10 +6365,10 @@
         <v>35947</v>
       </c>
       <c r="G68" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H68" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I68" s="10" t="s">
         <v>145</v>
@@ -6397,10 +6397,10 @@
         <v>35947</v>
       </c>
       <c r="G69" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H69" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I69" s="10" t="s">
         <v>145</v>
@@ -6429,10 +6429,10 @@
         <v>35947</v>
       </c>
       <c r="G70" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H70" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I70" s="10" t="s">
         <v>145</v>
@@ -6461,10 +6461,10 @@
         <v>35947</v>
       </c>
       <c r="G71" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H71" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I71" s="10" t="s">
         <v>145</v>
@@ -6493,10 +6493,10 @@
         <v>35947</v>
       </c>
       <c r="G72" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H72" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I72" s="10" t="s">
         <v>145</v>
@@ -6525,10 +6525,10 @@
         <v>35947</v>
       </c>
       <c r="G73" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H73" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I73" s="10" t="s">
         <v>145</v>
@@ -6557,10 +6557,10 @@
         <v>35947</v>
       </c>
       <c r="G74" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H74" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I74" s="10" t="s">
         <v>145</v>
@@ -6589,10 +6589,10 @@
         <v>35947</v>
       </c>
       <c r="G75" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H75" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I75" s="10" t="s">
         <v>145</v>
@@ -6621,10 +6621,10 @@
         <v>35947</v>
       </c>
       <c r="G76" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H76" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I76" s="10" t="s">
         <v>145</v>
@@ -6653,10 +6653,10 @@
         <v>35947</v>
       </c>
       <c r="G77" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H77" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I77" s="10" t="s">
         <v>145</v>
@@ -6685,10 +6685,10 @@
         <v>35947</v>
       </c>
       <c r="G78" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H78" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I78" s="10" t="s">
         <v>145</v>
@@ -6717,10 +6717,10 @@
         <v>35947</v>
       </c>
       <c r="G79" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H79" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I79" s="10" t="s">
         <v>145</v>
@@ -6749,10 +6749,10 @@
         <v>35947</v>
       </c>
       <c r="G80" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H80" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I80" s="10" t="s">
         <v>145</v>
@@ -6781,10 +6781,10 @@
         <v>35947</v>
       </c>
       <c r="G81" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H81" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I81" s="10" t="s">
         <v>145</v>
@@ -6813,10 +6813,10 @@
         <v>35947</v>
       </c>
       <c r="G82" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H82" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I82" s="10" t="s">
         <v>145</v>
@@ -6845,10 +6845,10 @@
         <v>35947</v>
       </c>
       <c r="G83" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H83" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I83" s="10" t="s">
         <v>145</v>
@@ -6877,10 +6877,10 @@
         <v>35947</v>
       </c>
       <c r="G84" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H84" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I84" s="10" t="s">
         <v>145</v>
@@ -6909,10 +6909,10 @@
         <v>35947</v>
       </c>
       <c r="G85" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H85" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I85" s="10" t="s">
         <v>145</v>
@@ -6941,10 +6941,10 @@
         <v>35947</v>
       </c>
       <c r="G86" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H86" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I86" s="10" t="s">
         <v>145</v>
@@ -6973,10 +6973,10 @@
         <v>35947</v>
       </c>
       <c r="G87" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H87" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I87" s="10" t="s">
         <v>145</v>
@@ -7005,10 +7005,10 @@
         <v>35947</v>
       </c>
       <c r="G88" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H88" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I88" s="10" t="s">
         <v>145</v>
@@ -7037,10 +7037,10 @@
         <v>35947</v>
       </c>
       <c r="G89" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H89" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I89" s="10" t="s">
         <v>145</v>
@@ -7069,10 +7069,10 @@
         <v>35947</v>
       </c>
       <c r="G90" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H90" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I90" s="10" t="s">
         <v>145</v>
@@ -7101,10 +7101,10 @@
         <v>35947</v>
       </c>
       <c r="G91" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H91" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I91" s="10" t="s">
         <v>145</v>
@@ -7133,10 +7133,10 @@
         <v>35947</v>
       </c>
       <c r="G92" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H92" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I92" s="10" t="s">
         <v>145</v>
@@ -7165,10 +7165,10 @@
         <v>35947</v>
       </c>
       <c r="G93" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H93" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I93" s="10" t="s">
         <v>145</v>
@@ -7197,10 +7197,10 @@
         <v>35947</v>
       </c>
       <c r="G94" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H94" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I94" s="10" t="s">
         <v>145</v>
@@ -7229,10 +7229,10 @@
         <v>35947</v>
       </c>
       <c r="G95" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H95" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I95" s="10" t="s">
         <v>145</v>
@@ -7261,10 +7261,10 @@
         <v>35947</v>
       </c>
       <c r="G96" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H96" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I96" s="10" t="s">
         <v>145</v>
@@ -7293,10 +7293,10 @@
         <v>35947</v>
       </c>
       <c r="G97" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H97" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I97" s="10" t="s">
         <v>145</v>
@@ -7325,10 +7325,10 @@
         <v>35947</v>
       </c>
       <c r="G98" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H98" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I98" s="10" t="s">
         <v>145</v>
@@ -7357,10 +7357,10 @@
         <v>35947</v>
       </c>
       <c r="G99" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H99" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I99" s="10" t="s">
         <v>145</v>
@@ -7483,7 +7483,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CK36"/>
+  <dimension ref="A1:CK38"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -9374,268 +9374,268 @@
         <v>94</v>
       </c>
       <c r="B8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="C8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="D8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="E8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="F8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="G8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="I8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="J8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="K8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="L8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="M8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="N8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="O8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="P8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="Q8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="R8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="S8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="T8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="U8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="V8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="W8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="X8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="Y8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="Z8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AA8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AB8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AC8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AD8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AE8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AF8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AG8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AH8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AI8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AJ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AK8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AL8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AM8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AN8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AO8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AP8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AQ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AR8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AS8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AT8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AU8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AV8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AW8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AX8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AY8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AZ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BA8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BB8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BC8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BD8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BE8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BF8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BG8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BH8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BI8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BJ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BK8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BL8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BM8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BN8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BO8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BP8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BQ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BR8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BS8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BT8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BU8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BV8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BW8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BX8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BY8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BZ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CA8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CB8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CC8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CD8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CE8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CF8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CG8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CH8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CI8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CJ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CK8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="9" spans="1:89" x14ac:dyDescent="0.2">
@@ -9643,268 +9643,268 @@
         <v>95</v>
       </c>
       <c r="B9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="U9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="V9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="X9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AB9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AC9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AD9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AJ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AN9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AV9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AW9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AZ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BF9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BG9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BH9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BI9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BJ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BK9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BL9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BM9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BN9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BO9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BP9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BQ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BR9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BS9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BT9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BU9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BV9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BW9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BX9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BZ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CA9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CB9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CC9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CD9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CE9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CF9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CG9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CH9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CI9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CJ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CK9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:89" x14ac:dyDescent="0.2">
@@ -17082,6 +17082,544 @@
         <v>3.5</v>
       </c>
     </row>
+    <row r="37" spans="1:89" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>45444</v>
+      </c>
+      <c r="B37" s="8">
+        <v>149</v>
+      </c>
+      <c r="C37" s="8">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="D37" s="8">
+        <v>157.5</v>
+      </c>
+      <c r="E37" s="8">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="F37" s="8">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="G37" s="8">
+        <v>145.1</v>
+      </c>
+      <c r="H37" s="8">
+        <v>146.5</v>
+      </c>
+      <c r="I37" s="8">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="J37" s="8">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="K37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="L37" s="8">
+        <v>143</v>
+      </c>
+      <c r="M37" s="8">
+        <v>148.4</v>
+      </c>
+      <c r="N37" s="8">
+        <v>143.5</v>
+      </c>
+      <c r="O37" s="8">
+        <v>149.80000000000001</v>
+      </c>
+      <c r="P37" s="8">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="Q37" s="8">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="R37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="S37" s="8">
+        <v>147.30000000000001</v>
+      </c>
+      <c r="T37" s="8">
+        <v>149</v>
+      </c>
+      <c r="U37" s="8">
+        <v>155.4</v>
+      </c>
+      <c r="V37" s="8">
+        <v>144.19999999999999</v>
+      </c>
+      <c r="W37" s="8">
+        <v>148.80000000000001</v>
+      </c>
+      <c r="X37" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="Y37" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="Z37" s="8">
+        <v>151.4</v>
+      </c>
+      <c r="AA37" s="8">
+        <v>149</v>
+      </c>
+      <c r="AB37" s="8">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="AC37" s="8">
+        <v>156.30000000000001</v>
+      </c>
+      <c r="AD37" s="8">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="AE37" s="8">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="AF37" s="8">
+        <v>145</v>
+      </c>
+      <c r="AG37" s="8">
+        <v>146.6</v>
+      </c>
+      <c r="AH37" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="AI37" s="8">
+        <v>143.69999999999999</v>
+      </c>
+      <c r="AJ37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="AK37" s="8">
+        <v>143.4</v>
+      </c>
+      <c r="AL37" s="8">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="AM37" s="8">
+        <v>143.69999999999999</v>
+      </c>
+      <c r="AN37" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="AO37" s="8">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="AP37" s="8">
+        <v>156</v>
+      </c>
+      <c r="AQ37" s="8">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="AR37" s="8">
+        <v>147.4</v>
+      </c>
+      <c r="AS37" s="8">
+        <v>149.5</v>
+      </c>
+      <c r="AT37" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="AU37" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="AV37" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="AW37" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AX37" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="AY37" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="AZ37" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="BA37" s="8">
+        <v>4</v>
+      </c>
+      <c r="BB37" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="BC37" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="BD37" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="BE37" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="BF37" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="BG37" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="BH37" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="BI37" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="BJ37" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="BK37" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="BL37" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="BM37" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="BN37" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="BO37" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="BP37" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="BQ37" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="BR37" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="BS37" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="BT37" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="BU37" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="BV37" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="BW37" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="BX37" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="BY37" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="BZ37" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="CA37" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="CB37" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CC37" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CD37" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="CE37" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="CF37" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CG37" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="CH37" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="CI37" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="CJ37" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CK37" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:89" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>45809</v>
+      </c>
+      <c r="B38" s="8">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="C38" s="8">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="D38" s="8">
+        <v>163.4</v>
+      </c>
+      <c r="E38" s="8">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="F38" s="8">
+        <v>153.1</v>
+      </c>
+      <c r="G38" s="8">
+        <v>149.6</v>
+      </c>
+      <c r="H38" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="I38" s="8">
+        <v>153.1</v>
+      </c>
+      <c r="J38" s="8">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="K38" s="8">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="L38" s="8">
+        <v>147.6</v>
+      </c>
+      <c r="M38" s="8">
+        <v>152.69999999999999</v>
+      </c>
+      <c r="N38" s="8">
+        <v>148.4</v>
+      </c>
+      <c r="O38" s="8">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="P38" s="8">
+        <v>160.4</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>165.8</v>
+      </c>
+      <c r="R38" s="8">
+        <v>155.6</v>
+      </c>
+      <c r="S38" s="8">
+        <v>151.9</v>
+      </c>
+      <c r="T38" s="8">
+        <v>154</v>
+      </c>
+      <c r="U38" s="8">
+        <v>164.4</v>
+      </c>
+      <c r="V38" s="8">
+        <v>150.19999999999999</v>
+      </c>
+      <c r="W38" s="8">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="X38" s="8">
+        <v>160.1</v>
+      </c>
+      <c r="Y38" s="8">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="Z38" s="8">
+        <v>156.6</v>
+      </c>
+      <c r="AA38" s="8">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="AB38" s="8">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="AC38" s="8">
+        <v>163.69999999999999</v>
+      </c>
+      <c r="AD38" s="8">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="AE38" s="8">
+        <v>153.1</v>
+      </c>
+      <c r="AF38" s="8">
+        <v>149.5</v>
+      </c>
+      <c r="AG38" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="AH38" s="8">
+        <v>154</v>
+      </c>
+      <c r="AI38" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="AJ38" s="8">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="AK38" s="8">
+        <v>148.1</v>
+      </c>
+      <c r="AL38" s="8">
+        <v>152.69999999999999</v>
+      </c>
+      <c r="AM38" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="AN38" s="8">
+        <v>153.9</v>
+      </c>
+      <c r="AO38" s="8">
+        <v>160.1</v>
+      </c>
+      <c r="AP38" s="8">
+        <v>161.5</v>
+      </c>
+      <c r="AQ38" s="8">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="AR38" s="8">
+        <v>152</v>
+      </c>
+      <c r="AS38" s="8">
+        <v>154.6</v>
+      </c>
+      <c r="AT38" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="AU38" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="AV38" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="AW38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="AX38" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="AY38" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="AZ38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="BA38" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="BB38" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="BC38" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="BD38" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="BE38" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="BF38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="BG38" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="BH38" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="BI38" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="BJ38" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="BK38" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="BL38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="BM38" s="8">
+        <v>5.8</v>
+      </c>
+      <c r="BN38" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="BO38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="BP38" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="BQ38" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="BR38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="BS38" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="BT38" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="BU38" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="BV38" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="BW38" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="BX38" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="BY38" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="BZ38" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="CA38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CB38" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="CC38" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="CD38" s="8">
+        <v>3</v>
+      </c>
+      <c r="CE38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CF38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="CG38" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="CH38" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="CI38" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="CJ38" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="CK38" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
